--- a/image processing/chapter2.xlsx
+++ b/image processing/chapter2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D 資料匣\課程\勤益課程\數位影像\PPT\授課版_(教師專用)\excel\chapter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D 資料匣\課程\勤益課程\數位影像\image processing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F450F6-4A8B-465C-83A3-725881B74C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6267B6B9-C06C-4F91-BB0B-FDE2E553F306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31370" yWindow="-2690" windowWidth="28800" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-6190" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="240">
   <si>
     <t>question</t>
   </si>
@@ -40,569 +40,704 @@
     <t>answer</t>
   </si>
   <si>
-    <t>影像矩陣中，每個元素代表什麼？</t>
-  </si>
-  <si>
-    <t>顏色名稱</t>
-  </si>
-  <si>
-    <t>檔案大小</t>
-  </si>
-  <si>
-    <t>座標</t>
-  </si>
-  <si>
-    <t>像素值</t>
-  </si>
-  <si>
-    <t>在數位影像中，鄰域處理通常使用什麼結構？</t>
-  </si>
-  <si>
-    <t>陣列</t>
-  </si>
-  <si>
-    <t>遮罩（Mask）</t>
-  </si>
-  <si>
-    <t>佇列</t>
-  </si>
-  <si>
-    <t>堆疊</t>
-  </si>
-  <si>
-    <t>3x3遮罩的中心像素有幾個鄰居？</t>
-  </si>
-  <si>
-    <t>4個</t>
-  </si>
-  <si>
-    <t>8個</t>
-  </si>
-  <si>
-    <t>6個</t>
-  </si>
-  <si>
-    <t>9個</t>
-  </si>
-  <si>
-    <t>影像的空間域處理是指？</t>
-  </si>
-  <si>
-    <t>直接對像素值操作</t>
-  </si>
-  <si>
-    <t>壓縮處理</t>
-  </si>
-  <si>
-    <t>格式轉換</t>
-  </si>
-  <si>
-    <t>頻率域轉換</t>
-  </si>
-  <si>
-    <t>影像的頻率域處理常用哪種轉換？</t>
-  </si>
-  <si>
-    <t>對數轉換</t>
-  </si>
-  <si>
-    <t>線性轉換</t>
-  </si>
-  <si>
-    <t>指數轉換</t>
-  </si>
-  <si>
-    <t>傅立葉轉換</t>
-  </si>
-  <si>
-    <t>點運算（Point Operation）是指？</t>
-  </si>
-  <si>
-    <t>處理整張影像</t>
-  </si>
-  <si>
-    <t>處理鄰域像素</t>
-  </si>
-  <si>
-    <t>只處理單一像素</t>
-  </si>
-  <si>
-    <t>處理多張影像</t>
-  </si>
-  <si>
-    <t>影像的負片效果是使用什麼運算？</t>
-  </si>
-  <si>
-    <t>減法</t>
-  </si>
-  <si>
-    <t>加法</t>
-  </si>
-  <si>
-    <t>反轉</t>
-  </si>
-  <si>
-    <t>乘法</t>
-  </si>
-  <si>
-    <t>影像增強的主要目的是？</t>
-  </si>
-  <si>
-    <t>轉換格式</t>
-  </si>
-  <si>
-    <t>加快處理速度</t>
-  </si>
-  <si>
-    <t>改善視覺效果</t>
-  </si>
-  <si>
-    <t>減少檔案大小</t>
-  </si>
-  <si>
-    <t>直方圖均化的目的是？</t>
-  </si>
-  <si>
-    <t>壓縮影像</t>
-  </si>
-  <si>
-    <t>銳化邊緣</t>
-  </si>
-  <si>
-    <t>去除雜訊</t>
-  </si>
-  <si>
-    <t>增強對比度</t>
-  </si>
-  <si>
-    <t>平滑濾波器主要用於？</t>
-  </si>
-  <si>
-    <t>銳化影像</t>
-  </si>
-  <si>
-    <t>影像分割</t>
-  </si>
-  <si>
-    <t>邊緣檢測</t>
-  </si>
-  <si>
-    <t>中值濾波器對哪種雜訊特別有效？</t>
-  </si>
-  <si>
-    <t>均勻雜訊</t>
-  </si>
-  <si>
-    <t>高斯雜訊</t>
-  </si>
-  <si>
-    <t>脈衝雜訊</t>
-  </si>
-  <si>
-    <t>椒鹽雜訊</t>
-  </si>
-  <si>
-    <t>拉普拉斯運算子主要用於？</t>
-  </si>
-  <si>
-    <t>影像壓縮</t>
-  </si>
-  <si>
-    <t>平滑影像</t>
-  </si>
-  <si>
-    <t>色彩轉換</t>
-  </si>
-  <si>
-    <t>Sobel運算子是一種？</t>
-  </si>
-  <si>
-    <t>雜訊產生器</t>
-  </si>
-  <si>
-    <t>平滑濾波器</t>
-  </si>
-  <si>
-    <t>壓縮演算法</t>
-  </si>
-  <si>
-    <t>邊緣檢測器</t>
-  </si>
-  <si>
-    <t>影像的梯度表示什麼？</t>
-  </si>
-  <si>
-    <t>亮度變化率</t>
-  </si>
-  <si>
-    <t>解析度</t>
-  </si>
-  <si>
-    <t>顏色變化</t>
-  </si>
-  <si>
-    <t>高通濾波器會保留影像的？</t>
-  </si>
-  <si>
-    <t>中頻成分</t>
-  </si>
-  <si>
-    <t>所有成分</t>
-  </si>
-  <si>
-    <t>高頻成分</t>
-  </si>
-  <si>
-    <t>低頻成分</t>
-  </si>
-  <si>
-    <t>低通濾波器的效果類似於？</t>
-  </si>
-  <si>
-    <t>邊緣增強</t>
-  </si>
-  <si>
-    <t>銳化</t>
-  </si>
-  <si>
-    <t>模糊</t>
-  </si>
-  <si>
-    <t>對比增強</t>
-  </si>
-  <si>
-    <t>影像的卷積運算主要用於？</t>
-  </si>
-  <si>
-    <t>濾波處理</t>
-  </si>
-  <si>
-    <t>解壓縮</t>
-  </si>
-  <si>
-    <t>壓縮</t>
-  </si>
-  <si>
-    <t>形態學處理中，膨脹運算會使物體？</t>
-  </si>
-  <si>
-    <t>變小</t>
-  </si>
-  <si>
-    <t>消失</t>
-  </si>
-  <si>
-    <t>變大</t>
-  </si>
-  <si>
-    <t>不變</t>
-  </si>
-  <si>
-    <t>形態學處理中，侵蝕運算會使物體？</t>
-  </si>
-  <si>
-    <t>分裂</t>
-  </si>
-  <si>
-    <t>開運算是指？</t>
-  </si>
-  <si>
-    <t>只做膨脹</t>
-  </si>
-  <si>
-    <t>先膨脹後侵蝕</t>
-  </si>
-  <si>
-    <t>只做侵蝕</t>
-  </si>
-  <si>
-    <t>先侵蝕後膨脹</t>
-  </si>
-  <si>
-    <t>閉運算是指？</t>
-  </si>
-  <si>
-    <t>影像二值化需要設定什麼？</t>
-  </si>
-  <si>
-    <t>閾值</t>
-  </si>
-  <si>
-    <t>壓縮率</t>
-  </si>
-  <si>
-    <t>色彩模式</t>
-  </si>
-  <si>
-    <t>Otsu方法用於？</t>
-  </si>
-  <si>
-    <t>手動設定閾值</t>
-  </si>
-  <si>
-    <t>影像旋轉</t>
-  </si>
-  <si>
-    <t>自動選擇閾值</t>
-  </si>
-  <si>
-    <t>影像分割的目的是？</t>
-  </si>
-  <si>
-    <t>調整大小</t>
-  </si>
-  <si>
-    <t>改變色彩</t>
-  </si>
-  <si>
-    <t>將影像分成不同區域</t>
-  </si>
-  <si>
-    <t>區域成長法是一種？</t>
-  </si>
-  <si>
-    <t>濾波方法</t>
-  </si>
-  <si>
-    <t>壓縮技術</t>
-  </si>
-  <si>
-    <t>影像的仿射轉換包括？</t>
-  </si>
-  <si>
-    <t>只有旋轉</t>
-  </si>
-  <si>
-    <t>只有縮放</t>
-  </si>
-  <si>
-    <t>只有平移</t>
-  </si>
-  <si>
-    <t>旋轉、縮放、平移</t>
-  </si>
-  <si>
-    <t>雙線性內插法用於？</t>
-  </si>
-  <si>
-    <t>雜訊去除</t>
-  </si>
-  <si>
-    <t>影像縮放</t>
-  </si>
-  <si>
-    <t>影像的幾何校正主要處理？</t>
-  </si>
-  <si>
-    <t>失真問題</t>
-  </si>
-  <si>
-    <t>壓縮問題</t>
-  </si>
-  <si>
-    <t>雜訊問題</t>
-  </si>
-  <si>
-    <t>色彩問題</t>
-  </si>
-  <si>
-    <t>霍夫轉換（Hough Transform）主要用於偵測？</t>
-  </si>
-  <si>
-    <t>紋理</t>
-  </si>
-  <si>
-    <t>直線和圓</t>
-  </si>
-  <si>
-    <t>雜訊</t>
-  </si>
-  <si>
-    <t>顏色</t>
-  </si>
-  <si>
-    <t>影像的連通性分析用於？</t>
-  </si>
-  <si>
-    <t>物件標記</t>
-  </si>
-  <si>
-    <t>色彩分析</t>
-  </si>
-  <si>
-    <t>4-連通是指像素與幾個鄰居相連？</t>
-  </si>
-  <si>
-    <t>2個</t>
-  </si>
-  <si>
-    <t>8-連通是指像素與幾個鄰居相連？</t>
-  </si>
-  <si>
-    <t>影像的紋理分析主要研究？</t>
-  </si>
-  <si>
-    <t>顏色分布</t>
-  </si>
-  <si>
-    <t>空間模式</t>
-  </si>
-  <si>
-    <t>灰度共生矩陣（GLCM）用於？</t>
-  </si>
-  <si>
-    <t>紋理特徵提取</t>
-  </si>
-  <si>
-    <t>影像的矩特徵可用於？</t>
-  </si>
-  <si>
-    <t>色彩校正</t>
-  </si>
-  <si>
-    <t>物件識別</t>
-  </si>
-  <si>
-    <t>Canny邊緣檢測器的優點是？</t>
-  </si>
-  <si>
-    <t>檢測準確</t>
-  </si>
-  <si>
-    <t>記憶體最少</t>
-  </si>
-  <si>
-    <t>最簡單</t>
-  </si>
-  <si>
-    <t>速度最快</t>
-  </si>
-  <si>
-    <t>影像的金字塔結構用於？</t>
-  </si>
-  <si>
-    <t>多尺度分析</t>
-  </si>
-  <si>
-    <t>高斯金字塔是透過什麼產生？</t>
-  </si>
-  <si>
-    <t>二值化</t>
-  </si>
-  <si>
-    <t>平滑和降採樣</t>
-  </si>
-  <si>
-    <t>拉普拉斯金字塔保留什麼資訊？</t>
-  </si>
-  <si>
-    <t>色彩</t>
-  </si>
-  <si>
-    <t>高頻細節</t>
-  </si>
-  <si>
-    <t>低頻</t>
-  </si>
-  <si>
-    <t>壓縮資訊</t>
-  </si>
-  <si>
-    <t>影像的頻譜分析可以觀察？</t>
-  </si>
-  <si>
-    <t>頻率成分</t>
-  </si>
-  <si>
-    <t>色彩分布</t>
-  </si>
-  <si>
-    <t>傅立葉轉換後，低頻成分代表？</t>
-  </si>
-  <si>
-    <t>邊緣</t>
-  </si>
-  <si>
-    <t>平滑區域</t>
-  </si>
-  <si>
-    <t>傅立葉轉換後，高頻成分代表？</t>
-  </si>
-  <si>
-    <t>背景</t>
-  </si>
-  <si>
-    <t>邊緣和細節</t>
-  </si>
-  <si>
-    <t>反銳化遮罩（Unsharp Masking）用於？</t>
-  </si>
-  <si>
-    <t>模糊影像</t>
-  </si>
-  <si>
-    <t>影像的對比度拉伸是一種？</t>
-  </si>
-  <si>
-    <t>幾何轉換</t>
-  </si>
-  <si>
-    <t>形態學處理</t>
-  </si>
-  <si>
-    <t>空間域處理</t>
-  </si>
-  <si>
-    <t>頻率域處理</t>
-  </si>
-  <si>
-    <t>伽瑪校正的參數γ&gt;1會使影像？</t>
-  </si>
-  <si>
-    <t>變暗</t>
-  </si>
-  <si>
-    <t>變亮</t>
-  </si>
-  <si>
-    <t>伽瑪校正的參數γ&lt;1會使影像？</t>
-  </si>
-  <si>
-    <t>影像的位元平面分解可以用於？</t>
-  </si>
-  <si>
-    <t>分析影像資訊分布</t>
-  </si>
-  <si>
-    <t>最高位元平面包含影像的？</t>
-  </si>
-  <si>
-    <t>主要資訊</t>
-  </si>
-  <si>
-    <t>細節</t>
-  </si>
-  <si>
-    <t>最低位元平面通常包含？</t>
-  </si>
-  <si>
-    <t>雜訊和細節</t>
-  </si>
-  <si>
-    <t>影像的同態濾波器用於？</t>
-  </si>
-  <si>
-    <t>同時處理照明和反射</t>
-  </si>
-  <si>
     <t>title</t>
-  </si>
-  <si>
-    <t>chapter_name</t>
   </si>
   <si>
     <t>影像處理</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>chapter_name</t>
+  </si>
+  <si>
+    <t>加快處理速度</t>
+  </si>
+  <si>
+    <t>減少檔案大小</t>
+  </si>
+  <si>
+    <t>在數位影像處理中,影像的本質與下列何者有密切關聯?</t>
+  </si>
+  <si>
+    <t>聲波輻射</t>
+  </si>
+  <si>
+    <t>電磁輻射</t>
+  </si>
+  <si>
+    <t>機械波動</t>
+  </si>
+  <si>
+    <t>熱輻射</t>
+  </si>
+  <si>
+    <t>根據普朗克方程式 E=h×f,能量E與下列何者成正比?</t>
+  </si>
+  <si>
+    <t>波長</t>
+  </si>
+  <si>
+    <t>振幅</t>
+  </si>
+  <si>
+    <t>頻率</t>
+  </si>
+  <si>
+    <t>速度</t>
+  </si>
+  <si>
+    <t>人眼視覺系統中,負責將光線轉化為神經訊號的結構是?</t>
+  </si>
+  <si>
+    <t>角膜</t>
+  </si>
+  <si>
+    <t>水晶體</t>
+  </si>
+  <si>
+    <t>視網膜</t>
+  </si>
+  <si>
+    <t>虹膜</t>
+  </si>
+  <si>
+    <t>人眼中的桿細胞(Rod Cells)主要負責什麼功能?</t>
+  </si>
+  <si>
+    <t>彩色視覺</t>
+  </si>
+  <si>
+    <t>低光照條件下的視覺</t>
+  </si>
+  <si>
+    <t>高解析度視覺</t>
+  </si>
+  <si>
+    <t>紫外線感知</t>
+  </si>
+  <si>
+    <t>人眼中負責彩色視覺的錐細胞有幾種?</t>
+  </si>
+  <si>
+    <t>兩種</t>
+  </si>
+  <si>
+    <t>三種</t>
+  </si>
+  <si>
+    <t>四種</t>
+  </si>
+  <si>
+    <t>五種</t>
+  </si>
+  <si>
+    <t>RGB色彩模型中的三原色不包括下列何者?</t>
+  </si>
+  <si>
+    <t>紅色</t>
+  </si>
+  <si>
+    <t>綠色</t>
+  </si>
+  <si>
+    <t>黃色</t>
+  </si>
+  <si>
+    <t>藍色</t>
+  </si>
+  <si>
+    <t>在8位元RGB模型中,每個顏色通道的強度範圍為何?</t>
+  </si>
+  <si>
+    <t>0至100</t>
+  </si>
+  <si>
+    <t>0至255</t>
+  </si>
+  <si>
+    <t>1至256</t>
+  </si>
+  <si>
+    <t>0至1024</t>
+  </si>
+  <si>
+    <t>純紅色在RGB色彩空間中的數值表示為?</t>
+  </si>
+  <si>
+    <t>(255, 0, 0)</t>
+  </si>
+  <si>
+    <t>(0, 255, 0)</t>
+  </si>
+  <si>
+    <t>(0, 0, 255)</t>
+  </si>
+  <si>
+    <t>(255, 255, 255)</t>
+  </si>
+  <si>
+    <t>CMYK色彩模型中的'K'代表什麼顏色?</t>
+  </si>
+  <si>
+    <t>洋紅</t>
+  </si>
+  <si>
+    <t>青色</t>
+  </si>
+  <si>
+    <t>黑色</t>
+  </si>
+  <si>
+    <t>CMYK色彩模型主要應用於下列哪個領域?</t>
+  </si>
+  <si>
+    <t>電視顯示</t>
+  </si>
+  <si>
+    <t>彩色印刷</t>
+  </si>
+  <si>
+    <t>網頁設計</t>
+  </si>
+  <si>
+    <t>手機螢幕</t>
+  </si>
+  <si>
+    <t>HSV色彩模型中,'H'代表什麼屬性?</t>
+  </si>
+  <si>
+    <t>明度</t>
+  </si>
+  <si>
+    <t>飽和度</t>
+  </si>
+  <si>
+    <t>色調</t>
+  </si>
+  <si>
+    <t>亮度</t>
+  </si>
+  <si>
+    <t>在HSV模型中,色調(Hue)通常表示為多少度的角度範圍?</t>
+  </si>
+  <si>
+    <t>0到180度</t>
+  </si>
+  <si>
+    <t>0到360度</t>
+  </si>
+  <si>
+    <t>0到90度</t>
+  </si>
+  <si>
+    <t>0到270度</t>
+  </si>
+  <si>
+    <t>JPEG的全名是什麼?</t>
+  </si>
+  <si>
+    <t>Joint Picture Experts Group</t>
+  </si>
+  <si>
+    <t>Joint Photographic Experts Group</t>
+  </si>
+  <si>
+    <t>Japan Photographic Experts Group</t>
+  </si>
+  <si>
+    <t>Joint Photo Engineering Group</t>
+  </si>
+  <si>
+    <t>JPEG主要使用哪種技術進行壓縮?</t>
+  </si>
+  <si>
+    <t>快速傅立葉轉換(FFT)</t>
+  </si>
+  <si>
+    <t>小波轉換(Wavelet)</t>
+  </si>
+  <si>
+    <t>離散餘弦轉換(DCT)</t>
+  </si>
+  <si>
+    <t>霍夫曼編碼</t>
+  </si>
+  <si>
+    <t>PNG的全名是什麼?</t>
+  </si>
+  <si>
+    <t>Portable Network Graphics</t>
+  </si>
+  <si>
+    <t>Picture Network Graphics</t>
+  </si>
+  <si>
+    <t>Portable New Graphics</t>
+  </si>
+  <si>
+    <t>Photo Network Group</t>
+  </si>
+  <si>
+    <t>GIF格式最多支援多少種顏色?</t>
+  </si>
+  <si>
+    <t>128色</t>
+  </si>
+  <si>
+    <t>256色</t>
+  </si>
+  <si>
+    <t>512色</t>
+  </si>
+  <si>
+    <t>1024色</t>
+  </si>
+  <si>
+    <t>GIF使用哪種壓縮演算法?</t>
+  </si>
+  <si>
+    <t>DCT</t>
+  </si>
+  <si>
+    <t>Huffman</t>
+  </si>
+  <si>
+    <t>Lempel-Ziv-Welch</t>
+  </si>
+  <si>
+    <t>Run-Length Encoding</t>
+  </si>
+  <si>
+    <t>BMP格式的主要特點是什麼?</t>
+  </si>
+  <si>
+    <t>高壓縮率</t>
+  </si>
+  <si>
+    <t>支援動畫</t>
+  </si>
+  <si>
+    <t>未經壓縮</t>
+  </si>
+  <si>
+    <t>支援透明度</t>
+  </si>
+  <si>
+    <t>在數位影像的座標系中,原點位於影像的哪個位置?</t>
+  </si>
+  <si>
+    <t>左下角</t>
+  </si>
+  <si>
+    <t>右上角</t>
+  </si>
+  <si>
+    <t>中心</t>
+  </si>
+  <si>
+    <t>左上角</t>
+  </si>
+  <si>
+    <t>在數位影像處理中,'取樣'主要是指什麼過程?</t>
+  </si>
+  <si>
+    <t>顏色的數位化</t>
+  </si>
+  <si>
+    <t>空間域的數位化</t>
+  </si>
+  <si>
+    <t>影像的壓縮</t>
+  </si>
+  <si>
+    <t>影像的增強</t>
+  </si>
+  <si>
+    <t>一張大小為n×m的RGB彩色影像,其張量維度應為?</t>
+  </si>
+  <si>
+    <t>n×m</t>
+  </si>
+  <si>
+    <t>n×m×2</t>
+  </si>
+  <si>
+    <t>n×m×3</t>
+  </si>
+  <si>
+    <t>n×m×4</t>
+  </si>
+  <si>
+    <t>RGB色彩模型屬於哪種混色方式?</t>
+  </si>
+  <si>
+    <t>減色混合</t>
+  </si>
+  <si>
+    <t>加色混合</t>
+  </si>
+  <si>
+    <t>中性混合</t>
+  </si>
+  <si>
+    <t>互補混合</t>
+  </si>
+  <si>
+    <t>CMYK是減色模型,這意味著當混合所有顏色時會得到什麼顏色?</t>
+  </si>
+  <si>
+    <t>白色</t>
+  </si>
+  <si>
+    <t>灰色</t>
+  </si>
+  <si>
+    <t>透明</t>
+  </si>
+  <si>
+    <t>從RGB轉換到CMY時,青色(C)的計算公式為?</t>
+  </si>
+  <si>
+    <t>C = R/255</t>
+  </si>
+  <si>
+    <t>C = 1 - R/255</t>
+  </si>
+  <si>
+    <t>C = 255 - R</t>
+  </si>
+  <si>
+    <t>C = R + 255</t>
+  </si>
+  <si>
+    <t>在CMYK模型中,K值(黑色)的計算方式為?</t>
+  </si>
+  <si>
+    <t>K = max(C, M, Y)</t>
+  </si>
+  <si>
+    <t>K = min(C, M, Y)</t>
+  </si>
+  <si>
+    <t>K = (C + M + Y)/3</t>
+  </si>
+  <si>
+    <t>K = C × M × Y</t>
+  </si>
+  <si>
+    <t>純青色在CMYK色彩空間中的數值表示為?</t>
+  </si>
+  <si>
+    <t>(0, 1, 0, 0)</t>
+  </si>
+  <si>
+    <t>(1, 0, 0, 0)</t>
+  </si>
+  <si>
+    <t>(0, 0, 1, 0)</t>
+  </si>
+  <si>
+    <t>(1, 1, 0, 0)</t>
+  </si>
+  <si>
+    <t>在HSV色彩模型中,紅色的色調角度範圍約為?</t>
+  </si>
+  <si>
+    <t>0°~60°</t>
+  </si>
+  <si>
+    <t>60°~120°</t>
+  </si>
+  <si>
+    <t>120°~180°</t>
+  </si>
+  <si>
+    <t>240°~300°</t>
+  </si>
+  <si>
+    <t>在HSV模型中,當飽和度為0%時,顏色呈現為?</t>
+  </si>
+  <si>
+    <t>HSV模型中,明度為100%表示什麼?</t>
+  </si>
+  <si>
+    <t>最暗的顏色</t>
+  </si>
+  <si>
+    <t>最亮的顏色</t>
+  </si>
+  <si>
+    <t>中等亮度</t>
+  </si>
+  <si>
+    <t>CIELAB色彩空間是由國際照明委員會在哪一年定義的?</t>
+  </si>
+  <si>
+    <t>1966年</t>
+  </si>
+  <si>
+    <t>1976年</t>
+  </si>
+  <si>
+    <t>1986年</t>
+  </si>
+  <si>
+    <t>1996年</t>
+  </si>
+  <si>
+    <t>在CIELAB色彩空間中,L*代表什麼?</t>
+  </si>
+  <si>
+    <t>對比度</t>
+  </si>
+  <si>
+    <t>CIELAB色彩空間中,a*軸的正值代表什麼顏色?</t>
+  </si>
+  <si>
+    <t>在CIELAB色彩空間中,b*的負值代表什麼顏色?</t>
+  </si>
+  <si>
+    <t>PNG格式使用的壓縮方式屬於?</t>
+  </si>
+  <si>
+    <t>有損壓縮</t>
+  </si>
+  <si>
+    <t>無損壓縮</t>
+  </si>
+  <si>
+    <t>部分有損</t>
+  </si>
+  <si>
+    <t>不壓縮</t>
+  </si>
+  <si>
+    <t>相較於GIF,PNG格式在透明度處理上的優勢是?</t>
+  </si>
+  <si>
+    <t>不支援透明</t>
+  </si>
+  <si>
+    <t>只支援完全透明</t>
+  </si>
+  <si>
+    <t>可進行更精細的透明度設定</t>
+  </si>
+  <si>
+    <t>透明度較差</t>
+  </si>
+  <si>
+    <t>PNG使用的'Deflate'壓縮算法也被用於哪種壓縮格式?</t>
+  </si>
+  <si>
+    <t>RAR</t>
+  </si>
+  <si>
+    <t>ZIP</t>
+  </si>
+  <si>
+    <t>7Z</t>
+  </si>
+  <si>
+    <t>TAR</t>
+  </si>
+  <si>
+    <t>GIF格式的最大特點是什麼?</t>
+  </si>
+  <si>
+    <t>高解析度</t>
+  </si>
+  <si>
+    <t>支援簡單動畫</t>
+  </si>
+  <si>
+    <t>檔案最小</t>
+  </si>
+  <si>
+    <t>色彩最豐富</t>
+  </si>
+  <si>
+    <t>TIFF格式廣泛應用於下列哪些領域?</t>
+  </si>
+  <si>
+    <t>遊戲開發</t>
+  </si>
+  <si>
+    <t>專業影像處理與出版印刷</t>
+  </si>
+  <si>
+    <t>社群媒體</t>
+  </si>
+  <si>
+    <t>RAW格式的主要優點是什麼?</t>
+  </si>
+  <si>
+    <t>保存最原始的影像資訊</t>
+  </si>
+  <si>
+    <t>處理速度最快</t>
+  </si>
+  <si>
+    <t>相容性最好</t>
+  </si>
+  <si>
+    <t>RAW格式的主要缺點是什麼?</t>
+  </si>
+  <si>
+    <t>畫質較差</t>
+  </si>
+  <si>
+    <t>不支援彩色</t>
+  </si>
+  <si>
+    <t>影像文件大小太大</t>
+  </si>
+  <si>
+    <t>無法編輯</t>
+  </si>
+  <si>
+    <t>關於人眼對亮度和對比的感知,下列敘述何者正確?</t>
+  </si>
+  <si>
+    <t>人眼對亮度的感知是線性的</t>
+  </si>
+  <si>
+    <t>人眼對亮度和對比的感知是非線性的</t>
+  </si>
+  <si>
+    <t>人眼只能感知高對比度</t>
+  </si>
+  <si>
+    <t>人眼對所有亮度等同敏感</t>
+  </si>
+  <si>
+    <t>人眼對於不同空間頻率的敏感度,下列何者最敏感?</t>
+  </si>
+  <si>
+    <t>低頻的平滑區域</t>
+  </si>
+  <si>
+    <t>中間頻率的紋理和邊緣</t>
+  </si>
+  <si>
+    <t>高頻的細小細節</t>
+  </si>
+  <si>
+    <t>所有頻率都相同</t>
+  </si>
+  <si>
+    <t>從RGB轉換到CIELAB色彩空間時,第一階段需要先轉換到哪個色彩空間?</t>
+  </si>
+  <si>
+    <t>HSV</t>
+  </si>
+  <si>
+    <t>CMYK</t>
+  </si>
+  <si>
+    <t>XYZ</t>
+  </si>
+  <si>
+    <t>YUV</t>
+  </si>
+  <si>
+    <t>CIELAB色彩空間的設計目的是?</t>
+  </si>
+  <si>
+    <t>在不同設備和照明條件下呈現一致的顏色</t>
+  </si>
+  <si>
+    <t>簡化色彩計算</t>
+  </si>
+  <si>
+    <t>BMP格式的結構主要由哪些部分組成?</t>
+  </si>
+  <si>
+    <t>僅有像素資料</t>
+  </si>
+  <si>
+    <t>檔案頭和像素資料</t>
+  </si>
+  <si>
+    <t>檔案頭、資訊頭、調色盤和像素資料</t>
+  </si>
+  <si>
+    <t>壓縮資料和索引</t>
+  </si>
+  <si>
+    <t>關於數位影像的座標系,下列敘述何者正確?</t>
+  </si>
+  <si>
+    <t>座標值可以是負數</t>
+  </si>
+  <si>
+    <t>座標值是非負整數</t>
+  </si>
+  <si>
+    <t>座標值可以是小數</t>
+  </si>
+  <si>
+    <t>座標值沒有限制</t>
+  </si>
+  <si>
+    <t>在數位影像處理中,取樣和量化的主要目的是?</t>
+  </si>
+  <si>
+    <t>增加影像解析度</t>
+  </si>
+  <si>
+    <t>將連續的影像資訊轉換為數位形式</t>
+  </si>
+  <si>
+    <t>減少雜訊</t>
+  </si>
+  <si>
+    <t>增強對比度</t>
+  </si>
+  <si>
+    <t>在量化過程中,量化函數Q的主要作用是?</t>
+  </si>
+  <si>
+    <t>放大影像</t>
+  </si>
+  <si>
+    <t>對像素強度值進行數位化</t>
+  </si>
+  <si>
+    <t>旋轉影像</t>
+  </si>
+  <si>
+    <t>平滑影像</t>
+  </si>
+  <si>
+    <t>國際色彩聯盟(ICC)的主要功能是?</t>
+  </si>
+  <si>
+    <t>開發新的色彩空間</t>
+  </si>
+  <si>
+    <t>進行不同色彩空間之間的轉換</t>
+  </si>
+  <si>
+    <t>壓縮影像檔案</t>
+  </si>
+  <si>
+    <t>設計影像格式</t>
+  </si>
+  <si>
+    <t>人眼中的三種錐細胞分別對應於哪三種顏色?</t>
+  </si>
+  <si>
+    <t>青、洋紅、黃</t>
+  </si>
+  <si>
+    <t>紅、綠、藍</t>
+  </si>
+  <si>
+    <t>紅、黃、藍</t>
+  </si>
+  <si>
+    <t>橙、綠、紫</t>
   </si>
   <si>
     <t>CH 02 數位影像基礎理論與實作</t>
@@ -975,16 +1110,16 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.75" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>193</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>192</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
@@ -1009,119 +1144,119 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -1129,59 +1264,59 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F11">
         <v>4</v>
@@ -1189,179 +1324,179 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F20">
         <v>3</v>
@@ -1369,139 +1504,139 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="E24" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="E25" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="E27" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="F27">
         <v>2</v>
@@ -1509,279 +1644,279 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="D28" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="E28" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="E29" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" t="s">
         <v>123</v>
       </c>
-      <c r="B30" t="s">
-        <v>124</v>
-      </c>
-      <c r="C30" t="s">
-        <v>125</v>
-      </c>
-      <c r="D30" t="s">
-        <v>126</v>
-      </c>
-      <c r="E30" t="s">
-        <v>127</v>
-      </c>
       <c r="F30">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="D31" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="E31" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B34" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>159</v>
       </c>
       <c r="C36" t="s">
-        <v>63</v>
+        <v>160</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>161</v>
       </c>
       <c r="E36" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B37" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="D37" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="E37" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="B38" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C38" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="D38" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="E38" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>174</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>175</v>
       </c>
       <c r="D39" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="E39" t="s">
-        <v>63</v>
+        <v>177</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="E40" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="B41" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C41" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="D41" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="E41" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="F41">
         <v>2</v>
@@ -1789,222 +1924,222 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="B42" t="s">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="C42" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="D42" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>190</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="B43" t="s">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="C43" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="E43" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="B44" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="C44" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D44" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="E44" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="F44">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>202</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>203</v>
       </c>
       <c r="D45" t="s">
-        <v>47</v>
+        <v>204</v>
       </c>
       <c r="E45" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="F45">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="B46" t="s">
-        <v>174</v>
+        <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="D46" t="s">
-        <v>176</v>
+        <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="F46">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="B47" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="C47" t="s">
-        <v>180</v>
+        <v>211</v>
       </c>
       <c r="D47" t="s">
-        <v>39</v>
+        <v>212</v>
       </c>
       <c r="E47" t="s">
-        <v>91</v>
+        <v>213</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="B48" t="s">
-        <v>91</v>
+        <v>215</v>
       </c>
       <c r="C48" t="s">
-        <v>39</v>
+        <v>216</v>
       </c>
       <c r="D48" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="E48" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="B49" t="s">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="C49" t="s">
-        <v>24</v>
+        <v>221</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>222</v>
       </c>
       <c r="E49" t="s">
-        <v>63</v>
+        <v>223</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="B50" t="s">
-        <v>185</v>
+        <v>225</v>
       </c>
       <c r="C50" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="E50" t="s">
-        <v>131</v>
+        <v>228</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="B51" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="C51" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="D51" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="E51" t="s">
-        <v>129</v>
+        <v>233</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="B52" t="s">
-        <v>190</v>
+        <v>235</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>236</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>237</v>
       </c>
       <c r="E52" t="s">
-        <v>86</v>
+        <v>238</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
